--- a/artfynd/A 17374-2026 artfynd.xlsx
+++ b/artfynd/A 17374-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63189073</v>
+        <v>63202034</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -739,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568938.9590187888</v>
+        <v>568939</v>
       </c>
       <c r="R2" t="n">
-        <v>6280487.116784973</v>
+        <v>6280487</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,19 +767,9 @@
           <t>2011-06-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -816,37 +801,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63202034</v>
+        <v>63189073</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -880,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568938.9590187888</v>
+        <v>568939</v>
       </c>
       <c r="R3" t="n">
-        <v>6280487.116784973</v>
+        <v>6280487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,19 +893,9 @@
           <t>2011-06-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 17374-2026 artfynd.xlsx
+++ b/artfynd/A 17374-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63202034</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,8 +934,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189073</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>